--- a/artfynd/A 56908-2025 artfynd.xlsx
+++ b/artfynd/A 56908-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1012,6 +1012,231 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129917919</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97660</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 56908, Mörghult, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>584176</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6401326</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På traktorvägen</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129917941</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 56908, Mörghult, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>584176</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6401326</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Bohål i några grova aspar</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56908-2025 artfynd.xlsx
+++ b/artfynd/A 56908-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>129907597</v>
       </c>
       <c r="B3" t="n">
-        <v>110705</v>
+        <v>110735</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129907658</v>
       </c>
       <c r="B4" t="n">
-        <v>110705</v>
+        <v>110735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>129917919</v>
       </c>
       <c r="B5" t="n">
-        <v>97660</v>
+        <v>97664</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56908-2025 artfynd.xlsx
+++ b/artfynd/A 56908-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129909705</v>
       </c>
       <c r="B2" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>129907597</v>
       </c>
       <c r="B3" t="n">
-        <v>110735</v>
+        <v>110739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129907658</v>
       </c>
       <c r="B4" t="n">
-        <v>110735</v>
+        <v>110739</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>129917919</v>
       </c>
       <c r="B5" t="n">
-        <v>97664</v>
+        <v>97668</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>129917941</v>
       </c>
       <c r="B6" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 56908-2025 artfynd.xlsx
+++ b/artfynd/A 56908-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129909705</v>
       </c>
       <c r="B2" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>129907597</v>
       </c>
       <c r="B3" t="n">
-        <v>110739</v>
+        <v>110742</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129907658</v>
       </c>
       <c r="B4" t="n">
-        <v>110739</v>
+        <v>110742</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>129917919</v>
       </c>
       <c r="B5" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>129917941</v>
       </c>
       <c r="B6" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 56908-2025 artfynd.xlsx
+++ b/artfynd/A 56908-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>129907597</v>
       </c>
       <c r="B3" t="n">
-        <v>110742</v>
+        <v>110743</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129907658</v>
       </c>
       <c r="B4" t="n">
-        <v>110742</v>
+        <v>110743</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>129917919</v>
       </c>
       <c r="B5" t="n">
-        <v>97671</v>
+        <v>97672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56908-2025 artfynd.xlsx
+++ b/artfynd/A 56908-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129909705</v>
       </c>
       <c r="B2" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>129907597</v>
       </c>
       <c r="B3" t="n">
-        <v>110743</v>
+        <v>110760</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129907658</v>
       </c>
       <c r="B4" t="n">
-        <v>110743</v>
+        <v>110760</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>129917919</v>
       </c>
       <c r="B5" t="n">
-        <v>97672</v>
+        <v>97689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56908-2025 artfynd.xlsx
+++ b/artfynd/A 56908-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>129907597</v>
       </c>
       <c r="B3" t="n">
-        <v>110776</v>
+        <v>110779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129907658</v>
       </c>
       <c r="B4" t="n">
-        <v>110776</v>
+        <v>110779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>129917919</v>
       </c>
       <c r="B5" t="n">
-        <v>97705</v>
+        <v>97707</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56908-2025 artfynd.xlsx
+++ b/artfynd/A 56908-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129909705</v>
       </c>
       <c r="B2" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>129907597</v>
       </c>
       <c r="B3" t="n">
-        <v>110779</v>
+        <v>110866</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129907658</v>
       </c>
       <c r="B4" t="n">
-        <v>110779</v>
+        <v>110866</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>129917919</v>
       </c>
       <c r="B5" t="n">
-        <v>97707</v>
+        <v>97794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>129917941</v>
       </c>
       <c r="B6" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 56908-2025 artfynd.xlsx
+++ b/artfynd/A 56908-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129909705</v>
       </c>
       <c r="B2" t="n">
-        <v>57985</v>
+        <v>57900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>129907597</v>
       </c>
       <c r="B3" t="n">
-        <v>110866</v>
+        <v>110779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129907658</v>
       </c>
       <c r="B4" t="n">
-        <v>110866</v>
+        <v>110779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>129917919</v>
       </c>
       <c r="B5" t="n">
-        <v>97794</v>
+        <v>97707</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>129917941</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>57738</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 56908-2025 artfynd.xlsx
+++ b/artfynd/A 56908-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129909705</v>
+        <v>129909738</v>
       </c>
       <c r="B2" t="n">
-        <v>57985</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,49 +686,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 56908, Mörghult, Sm</t>
+          <t>A 56370, Mörghult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584199</v>
+        <v>584026</v>
       </c>
       <c r="R2" t="n">
-        <v>6401319</v>
+        <v>6401334</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,12 +759,18 @@
           <t>2025-11-29</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gamla</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,17 +782,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129907597</v>
+        <v>129909724</v>
       </c>
       <c r="B3" t="n">
-        <v>110866</v>
+        <v>92567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,49 +800,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219677</v>
+        <v>6031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ängnässjön, Sm</t>
+          <t>A 56370, Mörghult, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584171</v>
+        <v>584039</v>
       </c>
       <c r="R3" t="n">
-        <v>6401322</v>
+        <v>6401314</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,11 +871,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Växer på en ek.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +886,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129907658</v>
+        <v>129917941</v>
       </c>
       <c r="B4" t="n">
-        <v>110866</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,49 +909,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219677</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ängnässjön, Sm</t>
+          <t>A 56908, Mörghult, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584161</v>
+        <v>584176</v>
       </c>
       <c r="R4" t="n">
-        <v>6401327</v>
+        <v>6401326</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,17 +971,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Växer på en ek.</t>
+          <t>Bohål i några grova aspar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,65 +990,64 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129917919</v>
+        <v>129909705</v>
       </c>
       <c r="B5" t="n">
-        <v>97794</v>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1061,13 +1055,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584176</v>
+        <v>584199</v>
       </c>
       <c r="R5" t="n">
-        <v>6401326</v>
+        <v>6401319</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,17 +1085,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På traktorvägen</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,7 +1099,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1122,17 +1110,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129917941</v>
+        <v>129909807</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,45 +1128,49 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 56908, Mörghult, Sm</t>
+          <t>A 56370, Mörghult, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584176</v>
+        <v>584042</v>
       </c>
       <c r="R6" t="n">
-        <v>6401326</v>
+        <v>6401325</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,17 +1194,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Bohål i några grova aspar</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,10 +1219,465 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129907597</v>
+      </c>
+      <c r="B7" t="n">
+        <v>111175</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ängnässjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>584171</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6401322</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Växer på en ek.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129907658</v>
+      </c>
+      <c r="B8" t="n">
+        <v>111175</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ängnässjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>584161</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6401327</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Växer på en ek.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129909748</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 56370, Mörghult, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>584042</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6401325</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129917919</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 56908, Mörghult, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>584176</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6401326</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På traktorvägen</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
           <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
